--- a/Table/Excel/Text_Quest.xlsx
+++ b/Table/Excel/Text_Quest.xlsx
@@ -1,82 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TokTak\Desktop\Local\Unity\LOTW\LOTW\Table\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63CD0CD8-E4A0-43A7-BD89-952093F02445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A2E44DAC-F2CA-47FD-8B2C-14CEBECC12ED}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Text_Quest" sheetId="1" r:id="rId1"/>
+    <sheet name="Text_Quest" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
-  <si>
-    <t>DataId</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Ko</t>
-  </si>
-  <si>
-    <t>En</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color rgb="FF808080"/>
       <sz val="11"/>
-      <color rgb="FF808080"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -92,20 +59,22 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -125,25 +94,85 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E016DE0-D7C0-476D-92FE-4DA9E23222EE}" name="Text_Quest" displayName="Text_Quest" ref="B2:E4" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="B2:E4" xr:uid="{4E016DE0-D7C0-476D-92FE-4DA9E23222EE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_Quest" displayName="Text_Quest" ref="B2:E19" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B2:E19"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{605BBBE2-23E5-4747-BEF3-67DD763CD5B4}" name="DataId"/>
-    <tableColumn id="2" xr3:uid="{3B03356B-E0AF-4996-BC04-E4A542E4C943}" name="Key" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{5CFDCECA-6842-48EB-A923-236FFF7ACDF0}" name="Ko" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{A79472C4-5173-488B-9528-42FCE9A675B7}" name="En" dataDxfId="1"/>
+    <tableColumn id="1" name="DataId"/>
+    <tableColumn id="2" name="Key" dataDxfId="3"/>
+    <tableColumn id="3" name="Ko" dataDxfId="2"/>
+    <tableColumn id="4" name="En" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -445,49 +474,313 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F4A30C2-08FA-439F-863B-815F8BA9BCD8}">
-  <dimension ref="B2:E3"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" customWidth="1"/>
-    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.25" style="1" bestFit="1" customWidth="1"/>
+    <col width="3.125" customWidth="1" style="3" min="1" max="1"/>
+    <col width="9.625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="7" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="6.25" bestFit="1" customWidth="1" style="1" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2" ht="16.5" customHeight="1" s="3">
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>DataId</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Ko</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>En</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16.5" customHeight="1" s="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>quest.1.title</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>사라진 마을의 보물</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>quest.1.summary</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>촌장님의 비밀 의뢰. 박물관의 보물이 사라졌다. 범인은 마을 주민 중 한 명이다.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>quest.101.title</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>얼굴 트기</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>quest.101.summary</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>검맨이 마을 주민들과 먼저 얼굴을 트라고 권했다.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>quest.102.title</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>줄넘기 상대</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>quest.102.summary</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>하늘이가 줄넘기를 같이 하자고 한다.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>quest.103.title</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>꽃집 손님 후기</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>quest.103.summary</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>꽃집 코끼리가 손님 후기를 모아 달라고 했다.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>quest.objective.1001</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>주민들의 알리바이를 모은다</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>quest.objective.1002</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>저녁에 바에 가 본다</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>quest.objective.1003</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>지그를 다시 만난다</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>quest.objective.1011</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>검맨과 인사한다</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>quest.objective.1012</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>광장 주민 세 명과 인사한다</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>quest.objective.1021</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>하늘이와 줄넘기를 한다</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>quest.objective.1031</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>손님 후기를 세 개 모은다</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>